--- a/Verify-Desk-Template.xlsx
+++ b/Verify-Desk-Template.xlsx
@@ -901,13 +901,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="44" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -931,26 +932,9 @@
           <t>ACTIVE</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Jimmar San Buenaventura</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>jimmar.sanbuenaventura@revconnexsolutions.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Manager</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>PIN</t>
         </is>
       </c>
     </row>
